--- a/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen anomalía congénita</t>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
     </row>
@@ -787,37 +788,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,58</t>
+          <t>0,23; 2,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,29; 2,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,81</t>
+          <t>0,32; 1,87</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,15; 1,3</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,73</t>
+          <t>0,06; 0,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,14</t>
+          <t>0,2; 1,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,61</t>
+          <t>0,13; 0,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,08; 0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,75</t>
+          <t>0,23; 0,76</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen anomalía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3134</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3019</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3943</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2742</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3604</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4664</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3879</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3218</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4156</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>477; 5526</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3094</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>643; 5876</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4275</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3476</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1394; 8083</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4009</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2256</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2376</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3840</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4572</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>478; 4211</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3526</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3792</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4208</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3376</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>633; 5188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>442; 5273</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>604; 5967</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>601; 5345</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4076</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1469; 8101</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1816; 8600</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1125; 6799</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11035</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,67</t>
+          <t>0,23; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,62</t>
+          <t>0,28; 2,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,87</t>
+          <t>0,34; 1,91</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,3</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,09; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,75</t>
+          <t>0,06; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,08; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,09</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,61</t>
+          <t>0,1; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,47</t>
+          <t>0,08; 0,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,76</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3134</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,32 +1432,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3019</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>0; 3619</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2742</t>
+          <t>0; 3135</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3604</t>
+          <t>0; 3277</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4664</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3879</t>
+          <t>0; 3660</t>
         </is>
       </c>
     </row>
@@ -1580,22 +1580,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4156</t>
+          <t>0; 4136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>477; 5526</t>
+          <t>476; 5329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3094</t>
+          <t>0; 3965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>643; 5876</t>
+          <t>638; 5607</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 3743</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1394; 8083</t>
+          <t>1473; 8251</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4009</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2256</t>
+          <t>0; 2037</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2376</t>
+          <t>0; 2753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3840</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4572</t>
+          <t>0; 4473</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 2478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>478; 4211</t>
+          <t>478; 4323</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 3373</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>633; 5188</t>
+          <t>633; 4664</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>442; 5273</t>
+          <t>437; 4903</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>604; 5967</t>
+          <t>484; 5665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>601; 5345</t>
+          <t>602; 6019</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4076</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1469; 8101</t>
+          <t>1383; 8190</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1816; 8600</t>
+          <t>1346; 8294</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1125; 6799</t>
+          <t>1103; 7333</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3278; 11035</t>
+          <t>3201; 11555</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1005-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,09</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,69</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,8</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,44</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,12</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,57</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,5</t>
+          <t>0,23; 2,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,91</t>
+          <t>0,31; 1,81</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,34</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,69</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,61</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,9</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,96</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,68</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,69</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,18; 1,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,83</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,06; 0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,1</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,59</t>
+          <t>0,1; 0,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,5</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,21; 0,75</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3463</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3202</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3989</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3813</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3328</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3038</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3619</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3135</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3277</t>
+          <t>0; 3016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 4069</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3660</t>
+          <t>0; 3366</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1840</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 3391</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476; 5329</t>
+          <t>0; 5609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3965</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>638; 5607</t>
+          <t>477; 5356</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5204</t>
+          <t>0; 4248</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3743</t>
+          <t>0; 3480</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1473; 8251</t>
+          <t>1342; 7793</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>479</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4362</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2037</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2753</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4378</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>0; 2423</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4473</t>
+          <t>0; 3969</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2478</t>
+          <t>0; 2211</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>478; 4323</t>
+          <t>477; 4636</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,29 +1906,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3517</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3329</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3955</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4068</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 3534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3373</t>
+          <t>0; 3490</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1968,27 +1968,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>633; 4664</t>
+          <t>602; 5793</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>437; 4903</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>484; 5665</t>
+          <t>1359; 8470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>602; 6019</t>
+          <t>632; 5742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4745</t>
+          <t>442; 5184</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1383; 8190</t>
+          <t>605; 5496</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1346; 8294</t>
+          <t>1373; 8619</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1103; 7333</t>
+          <t>1121; 7188</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3201; 11555</t>
+          <t>3054; 10897</t>
         </is>
       </c>
     </row>
